--- a/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-17.xlsx
@@ -5841,7 +5841,11 @@
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>HYBRID · THC · MACHINE TRIMMED (TO BE DETERMINED)</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
@@ -17865,7 +17869,11 @@
           <t>Wedding Cake</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>HYBRID · THC · MACHINE TRIMMED (TO BE DETERMINED)</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr"/>

--- a/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-17.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Initial_List_2026-09-17.xlsx
@@ -3600,7 +3600,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
